--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314622</v>
+        <v>131314649</v>
       </c>
       <c r="B2" t="n">
-        <v>91810</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626710</v>
+        <v>626421</v>
       </c>
       <c r="R2" t="n">
-        <v>6997373</v>
+        <v>6997282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -769,17 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314649</v>
+        <v>131314622</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>91813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626421</v>
+        <v>626710</v>
       </c>
       <c r="R3" t="n">
-        <v>6997282</v>
+        <v>6997373</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314642</v>
+        <v>131314623</v>
       </c>
       <c r="B5" t="n">
-        <v>92108</v>
+        <v>91813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626613</v>
+        <v>626620</v>
       </c>
       <c r="R5" t="n">
-        <v>6997411</v>
+        <v>6997401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314623</v>
+        <v>131314641</v>
       </c>
       <c r="B6" t="n">
-        <v>91810</v>
+        <v>57881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,26 +1091,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1118,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626620</v>
+        <v>626582</v>
       </c>
       <c r="R6" t="n">
-        <v>6997401</v>
+        <v>6997317</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,7 +1167,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1174,7 +1178,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1184,7 +1188,7 @@
         <v>131314626</v>
       </c>
       <c r="B7" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,10 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314641</v>
+        <v>131314642</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>92111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,31 +1297,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1325,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626582</v>
+        <v>626613</v>
       </c>
       <c r="R8" t="n">
-        <v>6997317</v>
+        <v>6997411</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,6 +1368,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1380,17 +1380,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131314624</v>
+        <v>131314637</v>
       </c>
       <c r="B9" t="n">
-        <v>91810</v>
+        <v>58043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,37 +1398,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626523</v>
+        <v>626497</v>
       </c>
       <c r="R9" t="n">
-        <v>6997310</v>
+        <v>6997277</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1458,18 +1471,27 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1481,17 +1503,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131314637</v>
+        <v>131314624</v>
       </c>
       <c r="B10" t="n">
-        <v>58043</v>
+        <v>91813</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,50 +1521,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626497</v>
+        <v>626523</v>
       </c>
       <c r="R10" t="n">
-        <v>6997277</v>
+        <v>6997310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,27 +1581,18 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314650</v>
+        <v>131314644</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>80310</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626380</v>
+        <v>626648</v>
       </c>
       <c r="R13" t="n">
-        <v>6997310</v>
+        <v>6997392</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,32 +1902,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131314644</v>
+        <v>131314650</v>
       </c>
       <c r="B14" t="n">
-        <v>80310</v>
+        <v>79245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626648</v>
+        <v>626380</v>
       </c>
       <c r="R14" t="n">
-        <v>6997392</v>
+        <v>6997310</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
         <v>131314625</v>
       </c>
       <c r="B16" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>131314621</v>
       </c>
       <c r="B18" t="n">
-        <v>91773</v>
+        <v>91776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314634</v>
+        <v>131314646</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,50 +3001,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626502</v>
+        <v>626616</v>
       </c>
       <c r="R24" t="n">
-        <v>6997289</v>
+        <v>6997427</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3074,19 +3058,9 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,17 +3080,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314646</v>
+        <v>131314634</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3124,34 +3098,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626616</v>
+        <v>626502</v>
       </c>
       <c r="R25" t="n">
-        <v>6997427</v>
+        <v>6997289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,9 +3171,19 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3424,7 +3424,7 @@
         <v>131314627</v>
       </c>
       <c r="B28" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314649</v>
+        <v>131314622</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>91814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626421</v>
+        <v>626710</v>
       </c>
       <c r="R2" t="n">
-        <v>6997282</v>
+        <v>6997373</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -765,17 +769,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314622</v>
+        <v>131314649</v>
       </c>
       <c r="B3" t="n">
-        <v>91813</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626710</v>
+        <v>626421</v>
       </c>
       <c r="R3" t="n">
-        <v>6997373</v>
+        <v>6997282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -982,7 +982,7 @@
         <v>131314623</v>
       </c>
       <c r="B5" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314641</v>
+        <v>131314626</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>91814</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,31 +1091,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1123,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626582</v>
+        <v>626613</v>
       </c>
       <c r="R6" t="n">
-        <v>6997317</v>
+        <v>6997411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,6 +1162,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1178,17 +1174,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314626</v>
+        <v>131314642</v>
       </c>
       <c r="B7" t="n">
-        <v>91813</v>
+        <v>92112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1192,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314642</v>
+        <v>131314641</v>
       </c>
       <c r="B8" t="n">
-        <v>92111</v>
+        <v>57881</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,26 +1293,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1324,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626613</v>
+        <v>626582</v>
       </c>
       <c r="R8" t="n">
-        <v>6997411</v>
+        <v>6997317</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,7 +1369,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1380,17 +1380,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131314637</v>
+        <v>131314624</v>
       </c>
       <c r="B9" t="n">
-        <v>58043</v>
+        <v>91814</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,50 +1398,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626497</v>
+        <v>626523</v>
       </c>
       <c r="R9" t="n">
-        <v>6997277</v>
+        <v>6997310</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,27 +1458,18 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1503,17 +1481,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131314624</v>
+        <v>131314637</v>
       </c>
       <c r="B10" t="n">
-        <v>91813</v>
+        <v>58043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,37 +1499,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626523</v>
+        <v>626497</v>
       </c>
       <c r="R10" t="n">
-        <v>6997310</v>
+        <v>6997277</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,18 +1572,27 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1604,39 +1604,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314652</v>
+        <v>131314644</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>80311</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626681</v>
+        <v>626648</v>
       </c>
       <c r="R11" t="n">
-        <v>6997376</v>
+        <v>6997392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314653</v>
+        <v>131314652</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626421</v>
+        <v>626681</v>
       </c>
       <c r="R12" t="n">
-        <v>6997267</v>
+        <v>6997376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,32 +1805,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314644</v>
+        <v>131314653</v>
       </c>
       <c r="B13" t="n">
-        <v>80310</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626648</v>
+        <v>626421</v>
       </c>
       <c r="R13" t="n">
-        <v>6997392</v>
+        <v>6997267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
         <v>131314650</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314648</v>
+        <v>131314625</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>91814</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,37 +2010,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626483</v>
+        <v>626433</v>
       </c>
       <c r="R15" t="n">
-        <v>6997313</v>
+        <v>6997263</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2081,7 +2078,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2093,17 +2089,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314625</v>
+        <v>131314648</v>
       </c>
       <c r="B16" t="n">
-        <v>91813</v>
+        <v>79246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2111,34 +2107,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626433</v>
+        <v>626483</v>
       </c>
       <c r="R16" t="n">
-        <v>6997263</v>
+        <v>6997313</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,6 +2178,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2190,45 +2190,44 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131314630</v>
+        <v>131314621</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>91777</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2236,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626458</v>
+        <v>626433</v>
       </c>
       <c r="R17" t="n">
-        <v>6997294</v>
+        <v>6997263</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2274,17 +2273,13 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack tall</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2303,37 +2298,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131314621</v>
+        <v>131314630</v>
       </c>
       <c r="B18" t="n">
-        <v>91776</v>
+        <v>57884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2341,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626433</v>
+        <v>626458</v>
       </c>
       <c r="R18" t="n">
-        <v>6997263</v>
+        <v>6997294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,13 +2375,17 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314636</v>
+        <v>131314631</v>
       </c>
       <c r="B19" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,42 +2415,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626574</v>
+        <v>626459</v>
       </c>
       <c r="R19" t="n">
-        <v>6997271</v>
+        <v>6997269</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,7 +2490,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2492,7 +2500,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2512,17 +2520,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314631</v>
+        <v>131314636</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,50 +2538,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626459</v>
+        <v>626574</v>
       </c>
       <c r="R20" t="n">
-        <v>6997269</v>
+        <v>6997271</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2645,7 +2645,7 @@
         <v>131314651</v>
       </c>
       <c r="B21" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>131314646</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>131314627</v>
       </c>
       <c r="B28" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>131314647</v>
       </c>
       <c r="B29" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314625</v>
+        <v>131314648</v>
       </c>
       <c r="B15" t="n">
-        <v>91814</v>
+        <v>79246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,34 +2010,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626433</v>
+        <v>626483</v>
       </c>
       <c r="R15" t="n">
-        <v>6997263</v>
+        <v>6997313</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,6 +2081,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2089,17 +2093,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314648</v>
+        <v>131314625</v>
       </c>
       <c r="B16" t="n">
-        <v>79246</v>
+        <v>91814</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,37 +2111,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626483</v>
+        <v>626433</v>
       </c>
       <c r="R16" t="n">
-        <v>6997313</v>
+        <v>6997263</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2179,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314646</v>
+        <v>131314634</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,34 +3001,50 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626616</v>
+        <v>626502</v>
       </c>
       <c r="R24" t="n">
-        <v>6997427</v>
+        <v>6997289</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3058,9 +3074,19 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3080,17 +3106,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314634</v>
+        <v>131314646</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3098,50 +3124,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626502</v>
+        <v>626616</v>
       </c>
       <c r="R25" t="n">
-        <v>6997289</v>
+        <v>6997427</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3171,19 +3181,9 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131314622</v>
       </c>
       <c r="B2" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131314649</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>131314632</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314623</v>
+        <v>131314641</v>
       </c>
       <c r="B5" t="n">
-        <v>91814</v>
+        <v>57883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,26 +990,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1017,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626620</v>
+        <v>626582</v>
       </c>
       <c r="R5" t="n">
-        <v>6997401</v>
+        <v>6997317</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1066,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1073,17 +1077,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314626</v>
+        <v>131314623</v>
       </c>
       <c r="B6" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626613</v>
+        <v>626620</v>
       </c>
       <c r="R6" t="n">
-        <v>6997411</v>
+        <v>6997401</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314642</v>
+        <v>131314626</v>
       </c>
       <c r="B7" t="n">
-        <v>92112</v>
+        <v>91816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1282,10 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314641</v>
+        <v>131314642</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>92114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,31 +1297,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1325,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626582</v>
+        <v>626613</v>
       </c>
       <c r="R8" t="n">
-        <v>6997317</v>
+        <v>6997411</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,6 +1368,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1390,7 +1390,7 @@
         <v>131314624</v>
       </c>
       <c r="B9" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>131314637</v>
       </c>
       <c r="B10" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,32 +1611,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314644</v>
+        <v>131314652</v>
       </c>
       <c r="B11" t="n">
-        <v>80311</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626648</v>
+        <v>626681</v>
       </c>
       <c r="R11" t="n">
-        <v>6997392</v>
+        <v>6997376</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314652</v>
+        <v>131314653</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626681</v>
+        <v>626421</v>
       </c>
       <c r="R12" t="n">
-        <v>6997376</v>
+        <v>6997267</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314653</v>
+        <v>131314650</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626421</v>
+        <v>626380</v>
       </c>
       <c r="R13" t="n">
-        <v>6997267</v>
+        <v>6997310</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,32 +1902,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131314650</v>
+        <v>131314644</v>
       </c>
       <c r="B14" t="n">
-        <v>79246</v>
+        <v>80313</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626380</v>
+        <v>626648</v>
       </c>
       <c r="R14" t="n">
-        <v>6997310</v>
+        <v>6997392</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,7 +2002,7 @@
         <v>131314648</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>131314625</v>
       </c>
       <c r="B16" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>131314621</v>
       </c>
       <c r="B17" t="n">
-        <v>91777</v>
+        <v>91779</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>131314630</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>131314631</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>131314636</v>
       </c>
       <c r="B20" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>131314651</v>
       </c>
       <c r="B21" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>131314629</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>131314635</v>
       </c>
       <c r="B23" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>131314634</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>131314646</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>131314633</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>131314640</v>
       </c>
       <c r="B27" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131314627</v>
+        <v>131314647</v>
       </c>
       <c r="B28" t="n">
-        <v>91814</v>
+        <v>79248</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626433</v>
+        <v>626607</v>
       </c>
       <c r="R28" t="n">
-        <v>6997299</v>
+        <v>6997322</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314647</v>
+        <v>131314627</v>
       </c>
       <c r="B29" t="n">
-        <v>79246</v>
+        <v>91816</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626607</v>
+        <v>626433</v>
       </c>
       <c r="R29" t="n">
-        <v>6997322</v>
+        <v>6997299</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,7 +3618,7 @@
         <v>131314638</v>
       </c>
       <c r="B30" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131314622</v>
       </c>
       <c r="B2" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131314649</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>131314632</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>131314641</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>131314623</v>
       </c>
       <c r="B6" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>131314626</v>
       </c>
       <c r="B7" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>131314642</v>
       </c>
       <c r="B8" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>131314624</v>
       </c>
       <c r="B9" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>131314637</v>
       </c>
       <c r="B10" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,32 +1611,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314652</v>
+        <v>131314644</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>80314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626681</v>
+        <v>626648</v>
       </c>
       <c r="R11" t="n">
-        <v>6997376</v>
+        <v>6997392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314653</v>
+        <v>131314652</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626421</v>
+        <v>626681</v>
       </c>
       <c r="R12" t="n">
-        <v>6997267</v>
+        <v>6997376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314650</v>
+        <v>131314653</v>
       </c>
       <c r="B13" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626380</v>
+        <v>626421</v>
       </c>
       <c r="R13" t="n">
-        <v>6997310</v>
+        <v>6997267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,32 +1902,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131314644</v>
+        <v>131314650</v>
       </c>
       <c r="B14" t="n">
-        <v>80313</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626648</v>
+        <v>626380</v>
       </c>
       <c r="R14" t="n">
-        <v>6997392</v>
+        <v>6997310</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314648</v>
+        <v>131314625</v>
       </c>
       <c r="B15" t="n">
-        <v>79248</v>
+        <v>91817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,37 +2010,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626483</v>
+        <v>626433</v>
       </c>
       <c r="R15" t="n">
-        <v>6997313</v>
+        <v>6997263</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2081,7 +2078,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2093,17 +2089,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314625</v>
+        <v>131314648</v>
       </c>
       <c r="B16" t="n">
-        <v>91816</v>
+        <v>79249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2111,34 +2107,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626433</v>
+        <v>626483</v>
       </c>
       <c r="R16" t="n">
-        <v>6997263</v>
+        <v>6997313</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,6 +2178,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2200,7 +2200,7 @@
         <v>131314621</v>
       </c>
       <c r="B17" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>131314630</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314631</v>
+        <v>131314636</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>58046</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,50 +2415,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626459</v>
+        <v>626574</v>
       </c>
       <c r="R19" t="n">
-        <v>6997269</v>
+        <v>6997271</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,7 +2482,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2500,7 +2492,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2520,17 +2512,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314636</v>
+        <v>131314631</v>
       </c>
       <c r="B20" t="n">
-        <v>58045</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,42 +2530,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626574</v>
+        <v>626459</v>
       </c>
       <c r="R20" t="n">
-        <v>6997271</v>
+        <v>6997269</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2645,7 +2645,7 @@
         <v>131314651</v>
       </c>
       <c r="B21" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314629</v>
+        <v>131314635</v>
       </c>
       <c r="B22" t="n">
-        <v>57886</v>
+        <v>58046</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626589</v>
+        <v>626410</v>
       </c>
       <c r="R22" t="n">
-        <v>6997262</v>
+        <v>6997293</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2835,12 +2835,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131314635</v>
+        <v>131314629</v>
       </c>
       <c r="B23" t="n">
-        <v>58045</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,21 +2873,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2918,10 +2913,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626410</v>
+        <v>626589</v>
       </c>
       <c r="R23" t="n">
-        <v>6997293</v>
+        <v>6997262</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,7 +2948,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2963,7 +2958,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2990,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314634</v>
+        <v>131314646</v>
       </c>
       <c r="B24" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,50 +3001,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626502</v>
+        <v>626616</v>
       </c>
       <c r="R24" t="n">
-        <v>6997289</v>
+        <v>6997427</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3074,19 +3058,9 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,17 +3080,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314646</v>
+        <v>131314634</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3124,34 +3098,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626616</v>
+        <v>626502</v>
       </c>
       <c r="R25" t="n">
-        <v>6997427</v>
+        <v>6997289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,9 +3171,19 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3213,7 +3213,7 @@
         <v>131314633</v>
       </c>
       <c r="B26" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>131314640</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131314647</v>
+        <v>131314627</v>
       </c>
       <c r="B28" t="n">
-        <v>79248</v>
+        <v>91817</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626607</v>
+        <v>626433</v>
       </c>
       <c r="R28" t="n">
-        <v>6997322</v>
+        <v>6997299</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314627</v>
+        <v>131314647</v>
       </c>
       <c r="B29" t="n">
-        <v>91816</v>
+        <v>79249</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626433</v>
+        <v>626607</v>
       </c>
       <c r="R29" t="n">
-        <v>6997299</v>
+        <v>6997322</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,7 +3618,7 @@
         <v>131314638</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314641</v>
+        <v>131314623</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>91817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,31 +990,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1022,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626582</v>
+        <v>626620</v>
       </c>
       <c r="R5" t="n">
-        <v>6997317</v>
+        <v>6997401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,6 +1061,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1077,14 +1073,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314623</v>
+        <v>131314626</v>
       </c>
       <c r="B6" t="n">
         <v>91817</v>
@@ -1122,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626620</v>
+        <v>626613</v>
       </c>
       <c r="R6" t="n">
-        <v>6997401</v>
+        <v>6997411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314626</v>
+        <v>131314642</v>
       </c>
       <c r="B7" t="n">
-        <v>91817</v>
+        <v>92115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1192,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314642</v>
+        <v>131314641</v>
       </c>
       <c r="B8" t="n">
-        <v>92115</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,26 +1293,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1324,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626613</v>
+        <v>626582</v>
       </c>
       <c r="R8" t="n">
-        <v>6997411</v>
+        <v>6997317</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,7 +1369,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2197,37 +2197,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131314621</v>
+        <v>131314630</v>
       </c>
       <c r="B17" t="n">
-        <v>91780</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2235,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626433</v>
+        <v>626458</v>
       </c>
       <c r="R17" t="n">
-        <v>6997263</v>
+        <v>6997294</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,13 +2274,17 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack tall</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2298,38 +2303,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131314630</v>
+        <v>131314621</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>91780</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2337,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626458</v>
+        <v>626433</v>
       </c>
       <c r="R18" t="n">
-        <v>6997294</v>
+        <v>6997263</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,17 +2379,13 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack tall</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314636</v>
+        <v>131314631</v>
       </c>
       <c r="B19" t="n">
-        <v>58046</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,42 +2415,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626574</v>
+        <v>626459</v>
       </c>
       <c r="R19" t="n">
-        <v>6997271</v>
+        <v>6997269</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,7 +2490,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2492,7 +2500,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2512,17 +2520,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314631</v>
+        <v>131314636</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>58046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,50 +2538,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626459</v>
+        <v>626574</v>
       </c>
       <c r="R20" t="n">
-        <v>6997269</v>
+        <v>6997271</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314635</v>
+        <v>131314629</v>
       </c>
       <c r="B22" t="n">
-        <v>58046</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626410</v>
+        <v>626589</v>
       </c>
       <c r="R22" t="n">
-        <v>6997293</v>
+        <v>6997262</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2835,7 +2835,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2862,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131314629</v>
+        <v>131314635</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>58046</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,21 +2878,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2913,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626589</v>
+        <v>626410</v>
       </c>
       <c r="R23" t="n">
-        <v>6997262</v>
+        <v>6997293</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,7 +2953,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2958,12 +2963,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314622</v>
+        <v>131314649</v>
       </c>
       <c r="B2" t="n">
-        <v>91817</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626710</v>
+        <v>626421</v>
       </c>
       <c r="R2" t="n">
-        <v>6997373</v>
+        <v>6997282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -769,17 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314649</v>
+        <v>131314622</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>91817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626421</v>
+        <v>626710</v>
       </c>
       <c r="R3" t="n">
-        <v>6997282</v>
+        <v>6997373</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314623</v>
+        <v>131314642</v>
       </c>
       <c r="B5" t="n">
-        <v>91817</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626620</v>
+        <v>626613</v>
       </c>
       <c r="R5" t="n">
-        <v>6997401</v>
+        <v>6997411</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314626</v>
+        <v>131314623</v>
       </c>
       <c r="B6" t="n">
         <v>91817</v>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626613</v>
+        <v>626620</v>
       </c>
       <c r="R6" t="n">
-        <v>6997411</v>
+        <v>6997401</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314642</v>
+        <v>131314626</v>
       </c>
       <c r="B7" t="n">
-        <v>92115</v>
+        <v>91817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,21 +1192,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131314624</v>
+        <v>131314637</v>
       </c>
       <c r="B9" t="n">
-        <v>91817</v>
+        <v>58046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,37 +1398,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626523</v>
+        <v>626497</v>
       </c>
       <c r="R9" t="n">
-        <v>6997310</v>
+        <v>6997277</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1458,18 +1471,27 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1481,17 +1503,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131314637</v>
+        <v>131314624</v>
       </c>
       <c r="B10" t="n">
-        <v>58046</v>
+        <v>91817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,50 +1521,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626497</v>
+        <v>626523</v>
       </c>
       <c r="R10" t="n">
-        <v>6997277</v>
+        <v>6997310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,27 +1581,18 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1604,39 +1604,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314644</v>
+        <v>131314653</v>
       </c>
       <c r="B11" t="n">
-        <v>80314</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626648</v>
+        <v>626421</v>
       </c>
       <c r="R11" t="n">
-        <v>6997392</v>
+        <v>6997267</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,32 +1708,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314652</v>
+        <v>131314644</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>80314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626681</v>
+        <v>626648</v>
       </c>
       <c r="R12" t="n">
-        <v>6997376</v>
+        <v>6997392</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314653</v>
+        <v>131314652</v>
       </c>
       <c r="B13" t="n">
         <v>79249</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626421</v>
+        <v>626681</v>
       </c>
       <c r="R13" t="n">
-        <v>6997267</v>
+        <v>6997376</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1999,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314625</v>
+        <v>131314648</v>
       </c>
       <c r="B15" t="n">
-        <v>91817</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,34 +2010,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626433</v>
+        <v>626483</v>
       </c>
       <c r="R15" t="n">
-        <v>6997263</v>
+        <v>6997313</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,6 +2081,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2089,17 +2093,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314648</v>
+        <v>131314625</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>91817</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,37 +2111,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626483</v>
+        <v>626433</v>
       </c>
       <c r="R16" t="n">
-        <v>6997313</v>
+        <v>6997263</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2179,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314646</v>
+        <v>131314634</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,34 +3001,50 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626616</v>
+        <v>626502</v>
       </c>
       <c r="R24" t="n">
-        <v>6997427</v>
+        <v>6997289</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3058,9 +3074,19 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3080,17 +3106,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314634</v>
+        <v>131314646</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3098,50 +3124,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626502</v>
+        <v>626616</v>
       </c>
       <c r="R25" t="n">
-        <v>6997289</v>
+        <v>6997427</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3171,19 +3181,9 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314649</v>
+        <v>131314622</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>91818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626421</v>
+        <v>626710</v>
       </c>
       <c r="R2" t="n">
-        <v>6997282</v>
+        <v>6997373</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -765,17 +769,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314622</v>
+        <v>131314649</v>
       </c>
       <c r="B3" t="n">
-        <v>91817</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626710</v>
+        <v>626421</v>
       </c>
       <c r="R3" t="n">
-        <v>6997373</v>
+        <v>6997282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -876,7 +876,7 @@
         <v>131314632</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314642</v>
+        <v>131314623</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>91818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626613</v>
+        <v>626620</v>
       </c>
       <c r="R5" t="n">
-        <v>6997411</v>
+        <v>6997401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314623</v>
+        <v>131314626</v>
       </c>
       <c r="B6" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626620</v>
+        <v>626613</v>
       </c>
       <c r="R6" t="n">
-        <v>6997401</v>
+        <v>6997411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314626</v>
+        <v>131314642</v>
       </c>
       <c r="B7" t="n">
-        <v>91817</v>
+        <v>92116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,21 +1192,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,7 +1285,7 @@
         <v>131314641</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131314637</v>
+        <v>131314624</v>
       </c>
       <c r="B9" t="n">
-        <v>58046</v>
+        <v>91818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,50 +1398,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626497</v>
+        <v>626523</v>
       </c>
       <c r="R9" t="n">
-        <v>6997277</v>
+        <v>6997310</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,27 +1458,18 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1503,17 +1481,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131314624</v>
+        <v>131314637</v>
       </c>
       <c r="B10" t="n">
-        <v>91817</v>
+        <v>58047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,37 +1499,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626523</v>
+        <v>626497</v>
       </c>
       <c r="R10" t="n">
-        <v>6997310</v>
+        <v>6997277</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,18 +1572,27 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1604,39 +1604,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314653</v>
+        <v>131314644</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>80315</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626421</v>
+        <v>626648</v>
       </c>
       <c r="R11" t="n">
-        <v>6997267</v>
+        <v>6997392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,32 +1708,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314644</v>
+        <v>131314652</v>
       </c>
       <c r="B12" t="n">
-        <v>80314</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626648</v>
+        <v>626681</v>
       </c>
       <c r="R12" t="n">
-        <v>6997392</v>
+        <v>6997376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314652</v>
+        <v>131314653</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626681</v>
+        <v>626421</v>
       </c>
       <c r="R13" t="n">
-        <v>6997376</v>
+        <v>6997267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
         <v>131314650</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314648</v>
+        <v>131314625</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>91818</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,37 +2010,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626483</v>
+        <v>626433</v>
       </c>
       <c r="R15" t="n">
-        <v>6997313</v>
+        <v>6997263</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2081,7 +2078,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2093,17 +2089,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314625</v>
+        <v>131314648</v>
       </c>
       <c r="B16" t="n">
-        <v>91817</v>
+        <v>79250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2111,34 +2107,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626433</v>
+        <v>626483</v>
       </c>
       <c r="R16" t="n">
-        <v>6997263</v>
+        <v>6997313</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,6 +2178,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2190,45 +2190,44 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131314630</v>
+        <v>131314621</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>91781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2236,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626458</v>
+        <v>626433</v>
       </c>
       <c r="R17" t="n">
-        <v>6997294</v>
+        <v>6997263</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2274,17 +2273,13 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack tall</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2303,37 +2298,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131314621</v>
+        <v>131314630</v>
       </c>
       <c r="B18" t="n">
-        <v>91780</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2341,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626433</v>
+        <v>626458</v>
       </c>
       <c r="R18" t="n">
-        <v>6997263</v>
+        <v>6997294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,13 +2375,17 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314631</v>
+        <v>131314636</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>58047</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,50 +2415,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626459</v>
+        <v>626574</v>
       </c>
       <c r="R19" t="n">
-        <v>6997269</v>
+        <v>6997271</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,7 +2482,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2500,7 +2492,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2520,17 +2512,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314636</v>
+        <v>131314631</v>
       </c>
       <c r="B20" t="n">
-        <v>58046</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,42 +2530,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626574</v>
+        <v>626459</v>
       </c>
       <c r="R20" t="n">
-        <v>6997271</v>
+        <v>6997269</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2645,7 +2645,7 @@
         <v>131314651</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314629</v>
+        <v>131314635</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>58047</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626589</v>
+        <v>626410</v>
       </c>
       <c r="R22" t="n">
-        <v>6997262</v>
+        <v>6997293</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2835,12 +2835,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131314635</v>
+        <v>131314629</v>
       </c>
       <c r="B23" t="n">
-        <v>58046</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,21 +2873,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2918,10 +2913,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626410</v>
+        <v>626589</v>
       </c>
       <c r="R23" t="n">
-        <v>6997293</v>
+        <v>6997262</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,7 +2948,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2963,7 +2958,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2990,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314634</v>
+        <v>131314646</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,50 +3001,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626502</v>
+        <v>626616</v>
       </c>
       <c r="R24" t="n">
-        <v>6997289</v>
+        <v>6997427</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3074,19 +3058,9 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,17 +3080,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314646</v>
+        <v>131314634</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3124,34 +3098,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626616</v>
+        <v>626502</v>
       </c>
       <c r="R25" t="n">
-        <v>6997427</v>
+        <v>6997289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,9 +3171,19 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3213,7 +3213,7 @@
         <v>131314633</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>131314640</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>131314627</v>
       </c>
       <c r="B28" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>131314647</v>
       </c>
       <c r="B29" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>131314638</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314623</v>
+        <v>131314641</v>
       </c>
       <c r="B5" t="n">
-        <v>91818</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,26 +990,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1017,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626620</v>
+        <v>626582</v>
       </c>
       <c r="R5" t="n">
-        <v>6997401</v>
+        <v>6997317</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1066,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1073,14 +1077,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314626</v>
+        <v>131314623</v>
       </c>
       <c r="B6" t="n">
         <v>91818</v>
@@ -1118,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626613</v>
+        <v>626620</v>
       </c>
       <c r="R6" t="n">
-        <v>6997411</v>
+        <v>6997401</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314642</v>
+        <v>131314626</v>
       </c>
       <c r="B7" t="n">
-        <v>92116</v>
+        <v>91818</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1282,10 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314641</v>
+        <v>131314642</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>92116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,31 +1297,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1325,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626582</v>
+        <v>626613</v>
       </c>
       <c r="R8" t="n">
-        <v>6997317</v>
+        <v>6997411</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,6 +1368,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1380,17 +1380,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131314624</v>
+        <v>131314637</v>
       </c>
       <c r="B9" t="n">
-        <v>91818</v>
+        <v>58047</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,37 +1398,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626523</v>
+        <v>626497</v>
       </c>
       <c r="R9" t="n">
-        <v>6997310</v>
+        <v>6997277</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1458,18 +1471,27 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1481,17 +1503,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131314637</v>
+        <v>131314624</v>
       </c>
       <c r="B10" t="n">
-        <v>58047</v>
+        <v>91818</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,50 +1521,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626497</v>
+        <v>626523</v>
       </c>
       <c r="R10" t="n">
-        <v>6997277</v>
+        <v>6997310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,27 +1581,18 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1604,39 +1604,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314644</v>
+        <v>131314652</v>
       </c>
       <c r="B11" t="n">
-        <v>80315</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626648</v>
+        <v>626681</v>
       </c>
       <c r="R11" t="n">
-        <v>6997392</v>
+        <v>6997376</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314652</v>
+        <v>131314653</v>
       </c>
       <c r="B12" t="n">
         <v>79250</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626681</v>
+        <v>626421</v>
       </c>
       <c r="R12" t="n">
-        <v>6997376</v>
+        <v>6997267</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314653</v>
+        <v>131314650</v>
       </c>
       <c r="B13" t="n">
         <v>79250</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626421</v>
+        <v>626380</v>
       </c>
       <c r="R13" t="n">
-        <v>6997267</v>
+        <v>6997310</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,32 +1902,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131314650</v>
+        <v>131314644</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>80315</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626380</v>
+        <v>626648</v>
       </c>
       <c r="R14" t="n">
-        <v>6997310</v>
+        <v>6997392</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2197,37 +2197,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131314621</v>
+        <v>131314630</v>
       </c>
       <c r="B17" t="n">
-        <v>91781</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2235,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626433</v>
+        <v>626458</v>
       </c>
       <c r="R17" t="n">
-        <v>6997263</v>
+        <v>6997294</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,13 +2274,17 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack tall</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2298,38 +2303,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131314630</v>
+        <v>131314621</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>91781</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2337,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626458</v>
+        <v>626433</v>
       </c>
       <c r="R18" t="n">
-        <v>6997294</v>
+        <v>6997263</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,17 +2379,13 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack tall</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314635</v>
+        <v>131314629</v>
       </c>
       <c r="B22" t="n">
-        <v>58047</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626410</v>
+        <v>626589</v>
       </c>
       <c r="R22" t="n">
-        <v>6997293</v>
+        <v>6997262</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2835,7 +2835,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2862,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131314629</v>
+        <v>131314635</v>
       </c>
       <c r="B23" t="n">
-        <v>57888</v>
+        <v>58047</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,21 +2878,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2913,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626589</v>
+        <v>626410</v>
       </c>
       <c r="R23" t="n">
-        <v>6997262</v>
+        <v>6997293</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,7 +2953,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2958,12 +2963,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2990,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314646</v>
+        <v>131314634</v>
       </c>
       <c r="B24" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,34 +3001,50 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626616</v>
+        <v>626502</v>
       </c>
       <c r="R24" t="n">
-        <v>6997427</v>
+        <v>6997289</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3058,9 +3074,19 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3080,17 +3106,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314634</v>
+        <v>131314646</v>
       </c>
       <c r="B25" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3098,50 +3124,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626502</v>
+        <v>626616</v>
       </c>
       <c r="R25" t="n">
-        <v>6997289</v>
+        <v>6997427</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3171,19 +3181,9 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -1387,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131314637</v>
+        <v>131314624</v>
       </c>
       <c r="B9" t="n">
-        <v>58047</v>
+        <v>91818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,50 +1398,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626497</v>
+        <v>626523</v>
       </c>
       <c r="R9" t="n">
-        <v>6997277</v>
+        <v>6997310</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,27 +1458,18 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1503,17 +1481,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131314624</v>
+        <v>131314637</v>
       </c>
       <c r="B10" t="n">
-        <v>91818</v>
+        <v>58047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,37 +1499,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626523</v>
+        <v>626497</v>
       </c>
       <c r="R10" t="n">
-        <v>6997310</v>
+        <v>6997277</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,18 +1572,27 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1604,39 +1604,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314652</v>
+        <v>131314644</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>80315</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626681</v>
+        <v>626648</v>
       </c>
       <c r="R11" t="n">
-        <v>6997376</v>
+        <v>6997392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314653</v>
+        <v>131314652</v>
       </c>
       <c r="B12" t="n">
         <v>79250</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626421</v>
+        <v>626681</v>
       </c>
       <c r="R12" t="n">
-        <v>6997267</v>
+        <v>6997376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314650</v>
+        <v>131314653</v>
       </c>
       <c r="B13" t="n">
         <v>79250</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626380</v>
+        <v>626421</v>
       </c>
       <c r="R13" t="n">
-        <v>6997310</v>
+        <v>6997267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,32 +1902,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131314644</v>
+        <v>131314650</v>
       </c>
       <c r="B14" t="n">
-        <v>80315</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626648</v>
+        <v>626380</v>
       </c>
       <c r="R14" t="n">
-        <v>6997392</v>
+        <v>6997310</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314622</v>
+        <v>131314649</v>
       </c>
       <c r="B2" t="n">
-        <v>91818</v>
+        <v>79253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626710</v>
+        <v>626421</v>
       </c>
       <c r="R2" t="n">
-        <v>6997373</v>
+        <v>6997282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -769,17 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314649</v>
+        <v>131314622</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>91821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626421</v>
+        <v>626710</v>
       </c>
       <c r="R3" t="n">
-        <v>6997282</v>
+        <v>6997373</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -876,7 +876,7 @@
         <v>131314632</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314641</v>
+        <v>131314623</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>91821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,31 +990,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1022,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626582</v>
+        <v>626620</v>
       </c>
       <c r="R5" t="n">
-        <v>6997317</v>
+        <v>6997401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,6 +1061,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1077,17 +1073,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314623</v>
+        <v>131314626</v>
       </c>
       <c r="B6" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626620</v>
+        <v>626613</v>
       </c>
       <c r="R6" t="n">
-        <v>6997401</v>
+        <v>6997411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314626</v>
+        <v>131314642</v>
       </c>
       <c r="B7" t="n">
-        <v>91818</v>
+        <v>92119</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1192,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314642</v>
+        <v>131314641</v>
       </c>
       <c r="B8" t="n">
-        <v>92116</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,26 +1293,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1324,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626613</v>
+        <v>626582</v>
       </c>
       <c r="R8" t="n">
-        <v>6997411</v>
+        <v>6997317</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,7 +1369,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1390,7 +1390,7 @@
         <v>131314624</v>
       </c>
       <c r="B9" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>131314637</v>
       </c>
       <c r="B10" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,32 +1611,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314644</v>
+        <v>131314652</v>
       </c>
       <c r="B11" t="n">
-        <v>80315</v>
+        <v>79253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626648</v>
+        <v>626681</v>
       </c>
       <c r="R11" t="n">
-        <v>6997392</v>
+        <v>6997376</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314652</v>
+        <v>131314653</v>
       </c>
       <c r="B12" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626681</v>
+        <v>626421</v>
       </c>
       <c r="R12" t="n">
-        <v>6997376</v>
+        <v>6997267</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314653</v>
+        <v>131314650</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626421</v>
+        <v>626380</v>
       </c>
       <c r="R13" t="n">
-        <v>6997267</v>
+        <v>6997310</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,32 +1902,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131314650</v>
+        <v>131314644</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>80318</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626380</v>
+        <v>626648</v>
       </c>
       <c r="R14" t="n">
-        <v>6997310</v>
+        <v>6997392</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,7 +2002,7 @@
         <v>131314625</v>
       </c>
       <c r="B15" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>131314648</v>
       </c>
       <c r="B16" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,38 +2197,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131314630</v>
+        <v>131314621</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>91784</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2236,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626458</v>
+        <v>626433</v>
       </c>
       <c r="R17" t="n">
-        <v>6997294</v>
+        <v>6997263</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2274,17 +2273,13 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack tall</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2303,37 +2298,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131314621</v>
+        <v>131314630</v>
       </c>
       <c r="B18" t="n">
-        <v>91781</v>
+        <v>57891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2341,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626433</v>
+        <v>626458</v>
       </c>
       <c r="R18" t="n">
-        <v>6997263</v>
+        <v>6997294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,13 +2375,17 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314636</v>
+        <v>131314631</v>
       </c>
       <c r="B19" t="n">
-        <v>58047</v>
+        <v>57891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,42 +2415,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626574</v>
+        <v>626459</v>
       </c>
       <c r="R19" t="n">
-        <v>6997271</v>
+        <v>6997269</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,7 +2490,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2492,7 +2500,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2512,17 +2520,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314631</v>
+        <v>131314636</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>58050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,50 +2538,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626459</v>
+        <v>626574</v>
       </c>
       <c r="R20" t="n">
-        <v>6997269</v>
+        <v>6997271</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2645,7 +2645,7 @@
         <v>131314651</v>
       </c>
       <c r="B21" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314629</v>
+        <v>131314635</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>58050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626589</v>
+        <v>626410</v>
       </c>
       <c r="R22" t="n">
-        <v>6997262</v>
+        <v>6997293</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2835,12 +2835,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131314635</v>
+        <v>131314629</v>
       </c>
       <c r="B23" t="n">
-        <v>58047</v>
+        <v>57891</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,21 +2873,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2918,10 +2913,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626410</v>
+        <v>626589</v>
       </c>
       <c r="R23" t="n">
-        <v>6997293</v>
+        <v>6997262</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,7 +2948,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2963,7 +2958,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2990,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314634</v>
+        <v>131314646</v>
       </c>
       <c r="B24" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,50 +3001,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626502</v>
+        <v>626616</v>
       </c>
       <c r="R24" t="n">
-        <v>6997289</v>
+        <v>6997427</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3074,19 +3058,9 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,17 +3080,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314646</v>
+        <v>131314634</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3124,34 +3098,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626616</v>
+        <v>626502</v>
       </c>
       <c r="R25" t="n">
-        <v>6997427</v>
+        <v>6997289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,9 +3171,19 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3213,7 +3213,7 @@
         <v>131314633</v>
       </c>
       <c r="B26" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>131314640</v>
       </c>
       <c r="B27" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>131314627</v>
       </c>
       <c r="B28" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>131314647</v>
       </c>
       <c r="B29" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>131314638</v>
       </c>
       <c r="B30" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314649</v>
+        <v>131314622</v>
       </c>
       <c r="B2" t="n">
-        <v>79253</v>
+        <v>91822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626421</v>
+        <v>626710</v>
       </c>
       <c r="R2" t="n">
-        <v>6997282</v>
+        <v>6997373</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -765,17 +769,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314622</v>
+        <v>131314649</v>
       </c>
       <c r="B3" t="n">
-        <v>91821</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626710</v>
+        <v>626421</v>
       </c>
       <c r="R3" t="n">
-        <v>6997373</v>
+        <v>6997282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -876,7 +876,7 @@
         <v>131314632</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>131314623</v>
       </c>
       <c r="B5" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>131314626</v>
       </c>
       <c r="B6" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>131314642</v>
       </c>
       <c r="B7" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>131314641</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>131314624</v>
       </c>
       <c r="B9" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>131314637</v>
       </c>
       <c r="B10" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>131314652</v>
       </c>
       <c r="B11" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>131314653</v>
       </c>
       <c r="B12" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>131314650</v>
       </c>
       <c r="B13" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>131314644</v>
       </c>
       <c r="B14" t="n">
-        <v>80318</v>
+        <v>80319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>131314625</v>
       </c>
       <c r="B15" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>131314648</v>
       </c>
       <c r="B16" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>131314621</v>
       </c>
       <c r="B17" t="n">
-        <v>91784</v>
+        <v>91785</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>131314630</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>131314631</v>
       </c>
       <c r="B19" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>131314636</v>
       </c>
       <c r="B20" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>131314651</v>
       </c>
       <c r="B21" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314635</v>
+        <v>131314629</v>
       </c>
       <c r="B22" t="n">
-        <v>58050</v>
+        <v>57892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626410</v>
+        <v>626589</v>
       </c>
       <c r="R22" t="n">
-        <v>6997293</v>
+        <v>6997262</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2835,7 +2835,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2862,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131314629</v>
+        <v>131314635</v>
       </c>
       <c r="B23" t="n">
-        <v>57891</v>
+        <v>58051</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,21 +2878,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2913,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626589</v>
+        <v>626410</v>
       </c>
       <c r="R23" t="n">
-        <v>6997262</v>
+        <v>6997293</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,7 +2953,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2958,12 +2963,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2993,7 +2993,7 @@
         <v>131314646</v>
       </c>
       <c r="B24" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>131314634</v>
       </c>
       <c r="B25" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>131314633</v>
       </c>
       <c r="B26" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>131314640</v>
       </c>
       <c r="B27" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131314627</v>
+        <v>131314647</v>
       </c>
       <c r="B28" t="n">
-        <v>91821</v>
+        <v>79254</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626433</v>
+        <v>626607</v>
       </c>
       <c r="R28" t="n">
-        <v>6997299</v>
+        <v>6997322</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314647</v>
+        <v>131314627</v>
       </c>
       <c r="B29" t="n">
-        <v>79253</v>
+        <v>91822</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626607</v>
+        <v>626433</v>
       </c>
       <c r="R29" t="n">
-        <v>6997322</v>
+        <v>6997299</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,7 +3618,7 @@
         <v>131314638</v>
       </c>
       <c r="B30" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131314622</v>
       </c>
       <c r="B2" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131314649</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>131314632</v>
       </c>
       <c r="B4" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>131314623</v>
       </c>
       <c r="B5" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>131314626</v>
       </c>
       <c r="B6" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>131314642</v>
       </c>
       <c r="B7" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>131314641</v>
       </c>
       <c r="B8" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>131314624</v>
       </c>
       <c r="B9" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>131314637</v>
       </c>
       <c r="B10" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314652</v>
+        <v>131314653</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626681</v>
+        <v>626421</v>
       </c>
       <c r="R11" t="n">
-        <v>6997376</v>
+        <v>6997267</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314653</v>
+        <v>131314652</v>
       </c>
       <c r="B12" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626421</v>
+        <v>626681</v>
       </c>
       <c r="R12" t="n">
-        <v>6997267</v>
+        <v>6997376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1808,7 +1808,7 @@
         <v>131314650</v>
       </c>
       <c r="B13" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>131314644</v>
       </c>
       <c r="B14" t="n">
-        <v>80319</v>
+        <v>80325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>131314625</v>
       </c>
       <c r="B15" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>131314648</v>
       </c>
       <c r="B16" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,37 +2197,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131314621</v>
+        <v>131314630</v>
       </c>
       <c r="B17" t="n">
-        <v>91785</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2235,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626433</v>
+        <v>626458</v>
       </c>
       <c r="R17" t="n">
-        <v>6997263</v>
+        <v>6997294</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,13 +2274,17 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack tall</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2298,38 +2303,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131314630</v>
+        <v>131314621</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>91791</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2337,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626458</v>
+        <v>626433</v>
       </c>
       <c r="R18" t="n">
-        <v>6997294</v>
+        <v>6997263</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,17 +2379,13 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack tall</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>131314631</v>
       </c>
       <c r="B19" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>131314636</v>
       </c>
       <c r="B20" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>131314651</v>
       </c>
       <c r="B21" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314629</v>
+        <v>131314635</v>
       </c>
       <c r="B22" t="n">
-        <v>57892</v>
+        <v>58057</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626589</v>
+        <v>626410</v>
       </c>
       <c r="R22" t="n">
-        <v>6997262</v>
+        <v>6997293</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2835,12 +2835,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131314635</v>
+        <v>131314629</v>
       </c>
       <c r="B23" t="n">
-        <v>58051</v>
+        <v>57898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,21 +2873,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2918,10 +2913,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626410</v>
+        <v>626589</v>
       </c>
       <c r="R23" t="n">
-        <v>6997293</v>
+        <v>6997262</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,7 +2948,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2963,7 +2958,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2993,7 +2993,7 @@
         <v>131314646</v>
       </c>
       <c r="B24" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>131314634</v>
       </c>
       <c r="B25" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>131314633</v>
       </c>
       <c r="B26" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>131314640</v>
       </c>
       <c r="B27" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131314647</v>
+        <v>131314627</v>
       </c>
       <c r="B28" t="n">
-        <v>79254</v>
+        <v>91828</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626607</v>
+        <v>626433</v>
       </c>
       <c r="R28" t="n">
-        <v>6997322</v>
+        <v>6997299</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314627</v>
+        <v>131314647</v>
       </c>
       <c r="B29" t="n">
-        <v>91822</v>
+        <v>79260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626433</v>
+        <v>626607</v>
       </c>
       <c r="R29" t="n">
-        <v>6997299</v>
+        <v>6997322</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,7 +3618,7 @@
         <v>131314638</v>
       </c>
       <c r="B30" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314623</v>
+        <v>131314641</v>
       </c>
       <c r="B5" t="n">
-        <v>91828</v>
+        <v>57895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,26 +990,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1017,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626620</v>
+        <v>626582</v>
       </c>
       <c r="R5" t="n">
-        <v>6997401</v>
+        <v>6997317</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1066,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1073,14 +1077,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314626</v>
+        <v>131314623</v>
       </c>
       <c r="B6" t="n">
         <v>91828</v>
@@ -1118,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626613</v>
+        <v>626620</v>
       </c>
       <c r="R6" t="n">
-        <v>6997411</v>
+        <v>6997401</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314642</v>
+        <v>131314626</v>
       </c>
       <c r="B7" t="n">
-        <v>92126</v>
+        <v>91828</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1282,10 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314641</v>
+        <v>131314642</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>92126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,31 +1297,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1325,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626582</v>
+        <v>626613</v>
       </c>
       <c r="R8" t="n">
-        <v>6997317</v>
+        <v>6997411</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,6 +1368,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314625</v>
+        <v>131314648</v>
       </c>
       <c r="B15" t="n">
-        <v>91828</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,34 +2010,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626433</v>
+        <v>626483</v>
       </c>
       <c r="R15" t="n">
-        <v>6997263</v>
+        <v>6997313</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,6 +2081,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2089,17 +2093,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314648</v>
+        <v>131314625</v>
       </c>
       <c r="B16" t="n">
-        <v>79260</v>
+        <v>91828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,37 +2111,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626483</v>
+        <v>626433</v>
       </c>
       <c r="R16" t="n">
-        <v>6997313</v>
+        <v>6997263</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2179,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2190,45 +2190,44 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131314630</v>
+        <v>131314621</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>91791</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2236,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626458</v>
+        <v>626433</v>
       </c>
       <c r="R17" t="n">
-        <v>6997294</v>
+        <v>6997263</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2274,17 +2273,13 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack tall</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2303,37 +2298,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131314621</v>
+        <v>131314630</v>
       </c>
       <c r="B18" t="n">
-        <v>91791</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2341,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626433</v>
+        <v>626458</v>
       </c>
       <c r="R18" t="n">
-        <v>6997263</v>
+        <v>6997294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,13 +2375,17 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314622</v>
+        <v>131314649</v>
       </c>
       <c r="B2" t="n">
-        <v>91828</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626710</v>
+        <v>626421</v>
       </c>
       <c r="R2" t="n">
-        <v>6997373</v>
+        <v>6997282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -769,17 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314649</v>
+        <v>131314622</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>91828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626421</v>
+        <v>626710</v>
       </c>
       <c r="R3" t="n">
-        <v>6997282</v>
+        <v>6997373</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314648</v>
+        <v>131314625</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>91828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,37 +2010,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626483</v>
+        <v>626433</v>
       </c>
       <c r="R15" t="n">
-        <v>6997313</v>
+        <v>6997263</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2081,7 +2078,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2093,17 +2089,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314625</v>
+        <v>131314648</v>
       </c>
       <c r="B16" t="n">
-        <v>91828</v>
+        <v>79260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2111,34 +2107,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626433</v>
+        <v>626483</v>
       </c>
       <c r="R16" t="n">
-        <v>6997263</v>
+        <v>6997313</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,6 +2178,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314635</v>
+        <v>131314629</v>
       </c>
       <c r="B22" t="n">
-        <v>58057</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626410</v>
+        <v>626589</v>
       </c>
       <c r="R22" t="n">
-        <v>6997293</v>
+        <v>6997262</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2835,7 +2835,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2862,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131314629</v>
+        <v>131314635</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>58057</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,21 +2878,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2913,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626589</v>
+        <v>626410</v>
       </c>
       <c r="R23" t="n">
-        <v>6997262</v>
+        <v>6997293</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,7 +2953,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2958,12 +2963,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2990,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314646</v>
+        <v>131314634</v>
       </c>
       <c r="B24" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,34 +3001,50 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626616</v>
+        <v>626502</v>
       </c>
       <c r="R24" t="n">
-        <v>6997427</v>
+        <v>6997289</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3058,9 +3074,19 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3080,17 +3106,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314634</v>
+        <v>131314646</v>
       </c>
       <c r="B25" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3098,50 +3124,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626502</v>
+        <v>626616</v>
       </c>
       <c r="R25" t="n">
-        <v>6997289</v>
+        <v>6997427</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3171,19 +3181,9 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131314627</v>
+        <v>131314647</v>
       </c>
       <c r="B28" t="n">
-        <v>91828</v>
+        <v>79260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626433</v>
+        <v>626607</v>
       </c>
       <c r="R28" t="n">
-        <v>6997299</v>
+        <v>6997322</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314647</v>
+        <v>131314627</v>
       </c>
       <c r="B29" t="n">
-        <v>79260</v>
+        <v>91828</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626607</v>
+        <v>626433</v>
       </c>
       <c r="R29" t="n">
-        <v>6997322</v>
+        <v>6997299</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -1999,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314625</v>
+        <v>131314648</v>
       </c>
       <c r="B15" t="n">
-        <v>91828</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,34 +2010,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626433</v>
+        <v>626483</v>
       </c>
       <c r="R15" t="n">
-        <v>6997263</v>
+        <v>6997313</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,6 +2081,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2089,17 +2093,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314648</v>
+        <v>131314625</v>
       </c>
       <c r="B16" t="n">
-        <v>79260</v>
+        <v>91828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,37 +2111,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626483</v>
+        <v>626433</v>
       </c>
       <c r="R16" t="n">
-        <v>6997313</v>
+        <v>6997263</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2179,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314649</v>
+        <v>131314622</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>91828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626421</v>
+        <v>626710</v>
       </c>
       <c r="R2" t="n">
-        <v>6997282</v>
+        <v>6997373</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -765,17 +769,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314622</v>
+        <v>131314649</v>
       </c>
       <c r="B3" t="n">
-        <v>91828</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626710</v>
+        <v>626421</v>
       </c>
       <c r="R3" t="n">
-        <v>6997373</v>
+        <v>6997282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314641</v>
+        <v>131314623</v>
       </c>
       <c r="B5" t="n">
-        <v>57895</v>
+        <v>91828</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,31 +990,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1022,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626582</v>
+        <v>626620</v>
       </c>
       <c r="R5" t="n">
-        <v>6997317</v>
+        <v>6997401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,6 +1061,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1077,14 +1073,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314623</v>
+        <v>131314626</v>
       </c>
       <c r="B6" t="n">
         <v>91828</v>
@@ -1122,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626620</v>
+        <v>626613</v>
       </c>
       <c r="R6" t="n">
-        <v>6997401</v>
+        <v>6997411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314626</v>
+        <v>131314641</v>
       </c>
       <c r="B7" t="n">
-        <v>91828</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,26 +1192,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1223,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626613</v>
+        <v>626582</v>
       </c>
       <c r="R7" t="n">
-        <v>6997411</v>
+        <v>6997317</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,7 +1268,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
         <v>131314642</v>
       </c>
       <c r="B8" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131314624</v>
+        <v>131314637</v>
       </c>
       <c r="B9" t="n">
-        <v>91828</v>
+        <v>58057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,37 +1398,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626523</v>
+        <v>626497</v>
       </c>
       <c r="R9" t="n">
-        <v>6997310</v>
+        <v>6997277</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1458,18 +1471,27 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1481,17 +1503,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131314637</v>
+        <v>131314624</v>
       </c>
       <c r="B10" t="n">
-        <v>58057</v>
+        <v>91828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,50 +1521,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626497</v>
+        <v>626523</v>
       </c>
       <c r="R10" t="n">
-        <v>6997277</v>
+        <v>6997310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,27 +1581,18 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314653</v>
+        <v>131314652</v>
       </c>
       <c r="B11" t="n">
         <v>79260</v>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626421</v>
+        <v>626681</v>
       </c>
       <c r="R11" t="n">
-        <v>6997267</v>
+        <v>6997376</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314652</v>
+        <v>131314653</v>
       </c>
       <c r="B12" t="n">
         <v>79260</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626681</v>
+        <v>626421</v>
       </c>
       <c r="R12" t="n">
-        <v>6997376</v>
+        <v>6997267</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1999,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314648</v>
+        <v>131314625</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>91828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,37 +2010,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626483</v>
+        <v>626433</v>
       </c>
       <c r="R15" t="n">
-        <v>6997313</v>
+        <v>6997263</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2081,7 +2078,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2093,17 +2089,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314625</v>
+        <v>131314648</v>
       </c>
       <c r="B16" t="n">
-        <v>91828</v>
+        <v>79260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2111,34 +2107,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626433</v>
+        <v>626483</v>
       </c>
       <c r="R16" t="n">
-        <v>6997263</v>
+        <v>6997313</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,6 +2178,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314631</v>
+        <v>131314636</v>
       </c>
       <c r="B19" t="n">
-        <v>57898</v>
+        <v>58057</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,50 +2415,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626459</v>
+        <v>626574</v>
       </c>
       <c r="R19" t="n">
-        <v>6997269</v>
+        <v>6997271</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,7 +2482,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2500,7 +2492,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2520,17 +2512,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314636</v>
+        <v>131314631</v>
       </c>
       <c r="B20" t="n">
-        <v>58057</v>
+        <v>57898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,42 +2530,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626574</v>
+        <v>626459</v>
       </c>
       <c r="R20" t="n">
-        <v>6997271</v>
+        <v>6997269</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314622</v>
+        <v>131314649</v>
       </c>
       <c r="B2" t="n">
-        <v>91828</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626710</v>
+        <v>626421</v>
       </c>
       <c r="R2" t="n">
-        <v>6997373</v>
+        <v>6997282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -769,17 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314649</v>
+        <v>131314622</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>91829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626421</v>
+        <v>626710</v>
       </c>
       <c r="R3" t="n">
-        <v>6997282</v>
+        <v>6997373</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -876,7 +876,7 @@
         <v>131314632</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314623</v>
+        <v>131314641</v>
       </c>
       <c r="B5" t="n">
-        <v>91828</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,26 +990,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1017,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626620</v>
+        <v>626582</v>
       </c>
       <c r="R5" t="n">
-        <v>6997401</v>
+        <v>6997317</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1066,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1073,17 +1077,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314626</v>
+        <v>131314623</v>
       </c>
       <c r="B6" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626613</v>
+        <v>626620</v>
       </c>
       <c r="R6" t="n">
-        <v>6997411</v>
+        <v>6997401</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314641</v>
+        <v>131314626</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>91829</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,31 +1196,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1224,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626582</v>
+        <v>626613</v>
       </c>
       <c r="R7" t="n">
-        <v>6997317</v>
+        <v>6997411</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,6 +1267,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
         <v>131314642</v>
       </c>
       <c r="B8" t="n">
-        <v>92127</v>
+        <v>92128</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131314637</v>
+        <v>131314624</v>
       </c>
       <c r="B9" t="n">
-        <v>58057</v>
+        <v>91829</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,50 +1398,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626497</v>
+        <v>626523</v>
       </c>
       <c r="R9" t="n">
-        <v>6997277</v>
+        <v>6997310</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,27 +1458,18 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1503,17 +1481,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131314624</v>
+        <v>131314637</v>
       </c>
       <c r="B10" t="n">
-        <v>91828</v>
+        <v>58058</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,37 +1499,50 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626523</v>
+        <v>626497</v>
       </c>
       <c r="R10" t="n">
-        <v>6997310</v>
+        <v>6997277</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,18 +1572,27 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1614,7 +1614,7 @@
         <v>131314652</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>131314653</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>131314650</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>131314644</v>
       </c>
       <c r="B14" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>131314625</v>
       </c>
       <c r="B15" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>131314648</v>
       </c>
       <c r="B16" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>131314621</v>
       </c>
       <c r="B17" t="n">
-        <v>91791</v>
+        <v>91792</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>131314630</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314636</v>
+        <v>131314631</v>
       </c>
       <c r="B19" t="n">
-        <v>58057</v>
+        <v>57899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,42 +2415,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626574</v>
+        <v>626459</v>
       </c>
       <c r="R19" t="n">
-        <v>6997271</v>
+        <v>6997269</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,7 +2490,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2492,7 +2500,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2512,17 +2520,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314631</v>
+        <v>131314636</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>58058</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,50 +2538,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626459</v>
+        <v>626574</v>
       </c>
       <c r="R20" t="n">
-        <v>6997269</v>
+        <v>6997271</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2645,7 +2645,7 @@
         <v>131314651</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314629</v>
+        <v>131314635</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>58058</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626589</v>
+        <v>626410</v>
       </c>
       <c r="R22" t="n">
-        <v>6997262</v>
+        <v>6997293</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2835,12 +2835,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131314635</v>
+        <v>131314629</v>
       </c>
       <c r="B23" t="n">
-        <v>58057</v>
+        <v>57899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,21 +2873,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2918,10 +2913,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626410</v>
+        <v>626589</v>
       </c>
       <c r="R23" t="n">
-        <v>6997293</v>
+        <v>6997262</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,7 +2948,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2963,7 +2958,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2990,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314634</v>
+        <v>131314646</v>
       </c>
       <c r="B24" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,50 +3001,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626502</v>
+        <v>626616</v>
       </c>
       <c r="R24" t="n">
-        <v>6997289</v>
+        <v>6997427</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3074,19 +3058,9 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,17 +3080,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314646</v>
+        <v>131314634</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3124,34 +3098,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626616</v>
+        <v>626502</v>
       </c>
       <c r="R25" t="n">
-        <v>6997427</v>
+        <v>6997289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,9 +3171,19 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3213,7 +3213,7 @@
         <v>131314633</v>
       </c>
       <c r="B26" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>131314640</v>
       </c>
       <c r="B27" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131314647</v>
+        <v>131314627</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>91829</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626607</v>
+        <v>626433</v>
       </c>
       <c r="R28" t="n">
-        <v>6997322</v>
+        <v>6997299</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314627</v>
+        <v>131314647</v>
       </c>
       <c r="B29" t="n">
-        <v>91828</v>
+        <v>79261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626433</v>
+        <v>626607</v>
       </c>
       <c r="R29" t="n">
-        <v>6997299</v>
+        <v>6997322</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,7 +3618,7 @@
         <v>131314638</v>
       </c>
       <c r="B30" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131314649</v>
       </c>
       <c r="B2" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131314622</v>
       </c>
       <c r="B3" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>131314632</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>131314641</v>
       </c>
       <c r="B5" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>131314623</v>
       </c>
       <c r="B6" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>131314626</v>
       </c>
       <c r="B7" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>131314642</v>
       </c>
       <c r="B8" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>131314624</v>
       </c>
       <c r="B9" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>131314637</v>
       </c>
       <c r="B10" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,32 +1611,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314652</v>
+        <v>131314644</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>80329</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626681</v>
+        <v>626648</v>
       </c>
       <c r="R11" t="n">
-        <v>6997376</v>
+        <v>6997392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314653</v>
+        <v>131314652</v>
       </c>
       <c r="B12" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626421</v>
+        <v>626681</v>
       </c>
       <c r="R12" t="n">
-        <v>6997267</v>
+        <v>6997376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314650</v>
+        <v>131314653</v>
       </c>
       <c r="B13" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626380</v>
+        <v>626421</v>
       </c>
       <c r="R13" t="n">
-        <v>6997310</v>
+        <v>6997267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,32 +1902,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131314644</v>
+        <v>131314650</v>
       </c>
       <c r="B14" t="n">
-        <v>80326</v>
+        <v>79264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626648</v>
+        <v>626380</v>
       </c>
       <c r="R14" t="n">
-        <v>6997392</v>
+        <v>6997310</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314625</v>
+        <v>131314648</v>
       </c>
       <c r="B15" t="n">
-        <v>91829</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,34 +2010,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626433</v>
+        <v>626483</v>
       </c>
       <c r="R15" t="n">
-        <v>6997263</v>
+        <v>6997313</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,6 +2081,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2089,17 +2093,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314648</v>
+        <v>131314625</v>
       </c>
       <c r="B16" t="n">
-        <v>79261</v>
+        <v>91832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,37 +2111,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626483</v>
+        <v>626433</v>
       </c>
       <c r="R16" t="n">
-        <v>6997313</v>
+        <v>6997263</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2179,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2200,7 +2200,7 @@
         <v>131314621</v>
       </c>
       <c r="B17" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>131314630</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314631</v>
+        <v>131314636</v>
       </c>
       <c r="B19" t="n">
-        <v>57899</v>
+        <v>58061</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,50 +2415,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626459</v>
+        <v>626574</v>
       </c>
       <c r="R19" t="n">
-        <v>6997269</v>
+        <v>6997271</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,7 +2482,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2500,7 +2492,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2520,17 +2512,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314636</v>
+        <v>131314631</v>
       </c>
       <c r="B20" t="n">
-        <v>58058</v>
+        <v>57902</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,42 +2530,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626574</v>
+        <v>626459</v>
       </c>
       <c r="R20" t="n">
-        <v>6997271</v>
+        <v>6997269</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2645,7 +2645,7 @@
         <v>131314651</v>
       </c>
       <c r="B21" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314635</v>
+        <v>131314629</v>
       </c>
       <c r="B22" t="n">
-        <v>58058</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>626410</v>
+        <v>626589</v>
       </c>
       <c r="R22" t="n">
-        <v>6997293</v>
+        <v>6997262</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2835,7 +2835,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Två födosökande individer varav en hona.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2862,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131314629</v>
+        <v>131314635</v>
       </c>
       <c r="B23" t="n">
-        <v>57899</v>
+        <v>58061</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,21 +2878,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2913,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>626589</v>
+        <v>626410</v>
       </c>
       <c r="R23" t="n">
-        <v>6997262</v>
+        <v>6997293</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,7 +2953,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2958,12 +2963,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Två födosökande individer varav en hona.</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2993,7 +2993,7 @@
         <v>131314646</v>
       </c>
       <c r="B24" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>131314634</v>
       </c>
       <c r="B25" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>131314633</v>
       </c>
       <c r="B26" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>131314640</v>
       </c>
       <c r="B27" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131314627</v>
+        <v>131314647</v>
       </c>
       <c r="B28" t="n">
-        <v>91829</v>
+        <v>79264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626433</v>
+        <v>626607</v>
       </c>
       <c r="R28" t="n">
-        <v>6997299</v>
+        <v>6997322</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314647</v>
+        <v>131314627</v>
       </c>
       <c r="B29" t="n">
-        <v>79261</v>
+        <v>91832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626607</v>
+        <v>626433</v>
       </c>
       <c r="R29" t="n">
-        <v>6997322</v>
+        <v>6997299</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,7 +3618,7 @@
         <v>131314638</v>
       </c>
       <c r="B30" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314649</v>
+        <v>131314622</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626421</v>
+        <v>626710</v>
       </c>
       <c r="R2" t="n">
-        <v>6997282</v>
+        <v>6997373</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -765,17 +769,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314622</v>
+        <v>131314649</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626710</v>
+        <v>626421</v>
       </c>
       <c r="R3" t="n">
-        <v>6997373</v>
+        <v>6997282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314641</v>
+        <v>131314623</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>91832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,31 +990,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1022,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626582</v>
+        <v>626620</v>
       </c>
       <c r="R5" t="n">
-        <v>6997317</v>
+        <v>6997401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,6 +1061,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1077,14 +1073,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314623</v>
+        <v>131314626</v>
       </c>
       <c r="B6" t="n">
         <v>91832</v>
@@ -1122,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626620</v>
+        <v>626613</v>
       </c>
       <c r="R6" t="n">
-        <v>6997401</v>
+        <v>6997411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314626</v>
+        <v>131314642</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>92131</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1192,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314642</v>
+        <v>131314641</v>
       </c>
       <c r="B8" t="n">
-        <v>92131</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,26 +1293,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1324,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626613</v>
+        <v>626582</v>
       </c>
       <c r="R8" t="n">
-        <v>6997411</v>
+        <v>6997317</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,7 +1369,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1380,17 +1380,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131314624</v>
+        <v>131314637</v>
       </c>
       <c r="B9" t="n">
-        <v>91832</v>
+        <v>58061</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,37 +1398,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626523</v>
+        <v>626497</v>
       </c>
       <c r="R9" t="n">
-        <v>6997310</v>
+        <v>6997277</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1458,18 +1471,27 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1481,17 +1503,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131314637</v>
+        <v>131314624</v>
       </c>
       <c r="B10" t="n">
-        <v>58061</v>
+        <v>91832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,50 +1521,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626497</v>
+        <v>626523</v>
       </c>
       <c r="R10" t="n">
-        <v>6997277</v>
+        <v>6997310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,27 +1581,18 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1604,39 +1604,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314644</v>
+        <v>131314652</v>
       </c>
       <c r="B11" t="n">
-        <v>80329</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626648</v>
+        <v>626681</v>
       </c>
       <c r="R11" t="n">
-        <v>6997392</v>
+        <v>6997376</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314652</v>
+        <v>131314653</v>
       </c>
       <c r="B12" t="n">
         <v>79264</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626681</v>
+        <v>626421</v>
       </c>
       <c r="R12" t="n">
-        <v>6997376</v>
+        <v>6997267</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314653</v>
+        <v>131314650</v>
       </c>
       <c r="B13" t="n">
         <v>79264</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626421</v>
+        <v>626380</v>
       </c>
       <c r="R13" t="n">
-        <v>6997267</v>
+        <v>6997310</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,32 +1902,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131314650</v>
+        <v>131314644</v>
       </c>
       <c r="B14" t="n">
-        <v>79264</v>
+        <v>80329</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626380</v>
+        <v>626648</v>
       </c>
       <c r="R14" t="n">
-        <v>6997310</v>
+        <v>6997392</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314648</v>
+        <v>131314625</v>
       </c>
       <c r="B15" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,37 +2010,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626483</v>
+        <v>626433</v>
       </c>
       <c r="R15" t="n">
-        <v>6997313</v>
+        <v>6997263</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2081,7 +2078,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2093,17 +2089,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314625</v>
+        <v>131314648</v>
       </c>
       <c r="B16" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2111,34 +2107,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626433</v>
+        <v>626483</v>
       </c>
       <c r="R16" t="n">
-        <v>6997263</v>
+        <v>6997313</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,6 +2178,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314646</v>
+        <v>131314634</v>
       </c>
       <c r="B24" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,34 +3001,50 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626616</v>
+        <v>626502</v>
       </c>
       <c r="R24" t="n">
-        <v>6997427</v>
+        <v>6997289</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3058,9 +3074,19 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3080,17 +3106,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314634</v>
+        <v>131314646</v>
       </c>
       <c r="B25" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3098,50 +3124,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626502</v>
+        <v>626616</v>
       </c>
       <c r="R25" t="n">
-        <v>6997289</v>
+        <v>6997427</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3171,19 +3181,9 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131314647</v>
+        <v>131314627</v>
       </c>
       <c r="B28" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626607</v>
+        <v>626433</v>
       </c>
       <c r="R28" t="n">
-        <v>6997322</v>
+        <v>6997299</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314627</v>
+        <v>131314647</v>
       </c>
       <c r="B29" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626433</v>
+        <v>626607</v>
       </c>
       <c r="R29" t="n">
-        <v>6997299</v>
+        <v>6997322</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314622</v>
+        <v>131314649</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626710</v>
+        <v>626421</v>
       </c>
       <c r="R2" t="n">
-        <v>6997373</v>
+        <v>6997282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -769,17 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314649</v>
+        <v>131314622</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626421</v>
+        <v>626710</v>
       </c>
       <c r="R3" t="n">
-        <v>6997282</v>
+        <v>6997373</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1181,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314642</v>
+        <v>131314641</v>
       </c>
       <c r="B7" t="n">
-        <v>92131</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,26 +1192,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1219,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626613</v>
+        <v>626582</v>
       </c>
       <c r="R7" t="n">
-        <v>6997411</v>
+        <v>6997317</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1263,7 +1268,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1275,17 +1279,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314641</v>
+        <v>131314642</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>92131</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,31 +1297,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1325,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626582</v>
+        <v>626613</v>
       </c>
       <c r="R8" t="n">
-        <v>6997317</v>
+        <v>6997411</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,6 +1368,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1611,32 +1611,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314652</v>
+        <v>131314644</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>80329</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626681</v>
+        <v>626648</v>
       </c>
       <c r="R11" t="n">
-        <v>6997376</v>
+        <v>6997392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314653</v>
+        <v>131314652</v>
       </c>
       <c r="B12" t="n">
         <v>79264</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626421</v>
+        <v>626681</v>
       </c>
       <c r="R12" t="n">
-        <v>6997267</v>
+        <v>6997376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314650</v>
+        <v>131314653</v>
       </c>
       <c r="B13" t="n">
         <v>79264</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626380</v>
+        <v>626421</v>
       </c>
       <c r="R13" t="n">
-        <v>6997310</v>
+        <v>6997267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,32 +1902,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131314644</v>
+        <v>131314650</v>
       </c>
       <c r="B14" t="n">
-        <v>80329</v>
+        <v>79264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626648</v>
+        <v>626380</v>
       </c>
       <c r="R14" t="n">
-        <v>6997392</v>
+        <v>6997310</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2990,10 +2990,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314634</v>
+        <v>131314646</v>
       </c>
       <c r="B24" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,50 +3001,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>626502</v>
+        <v>626616</v>
       </c>
       <c r="R24" t="n">
-        <v>6997289</v>
+        <v>6997427</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3074,19 +3058,9 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,17 +3080,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314646</v>
+        <v>131314634</v>
       </c>
       <c r="B25" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3124,34 +3098,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>626616</v>
+        <v>626502</v>
       </c>
       <c r="R25" t="n">
-        <v>6997427</v>
+        <v>6997289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,9 +3171,19 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131314627</v>
+        <v>131314647</v>
       </c>
       <c r="B28" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626433</v>
+        <v>626607</v>
       </c>
       <c r="R28" t="n">
-        <v>6997299</v>
+        <v>6997322</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314647</v>
+        <v>131314627</v>
       </c>
       <c r="B29" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626607</v>
+        <v>626433</v>
       </c>
       <c r="R29" t="n">
-        <v>6997322</v>
+        <v>6997299</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -1181,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314641</v>
+        <v>131314642</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>92131</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,31 +1192,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1224,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626582</v>
+        <v>626613</v>
       </c>
       <c r="R7" t="n">
-        <v>6997317</v>
+        <v>6997411</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,6 +1263,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1279,17 +1275,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314642</v>
+        <v>131314641</v>
       </c>
       <c r="B8" t="n">
-        <v>92131</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,26 +1293,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1324,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626613</v>
+        <v>626582</v>
       </c>
       <c r="R8" t="n">
-        <v>6997411</v>
+        <v>6997317</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,7 +1369,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314625</v>
+        <v>131314648</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,34 +2010,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626433</v>
+        <v>626483</v>
       </c>
       <c r="R15" t="n">
-        <v>6997263</v>
+        <v>6997313</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2078,6 +2081,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2089,17 +2093,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314648</v>
+        <v>131314625</v>
       </c>
       <c r="B16" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,37 +2111,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626483</v>
+        <v>626433</v>
       </c>
       <c r="R16" t="n">
-        <v>6997313</v>
+        <v>6997263</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2178,7 +2179,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314649</v>
+        <v>131314622</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626421</v>
+        <v>626710</v>
       </c>
       <c r="R2" t="n">
-        <v>6997282</v>
+        <v>6997373</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -765,17 +769,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314622</v>
+        <v>131314649</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626710</v>
+        <v>626421</v>
       </c>
       <c r="R3" t="n">
-        <v>6997373</v>
+        <v>6997282</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -876,7 +876,7 @@
         <v>131314632</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314623</v>
+        <v>131314641</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>57901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,26 +990,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1017,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626620</v>
+        <v>626582</v>
       </c>
       <c r="R5" t="n">
-        <v>6997401</v>
+        <v>6997317</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1066,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1073,17 +1077,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314626</v>
+        <v>131314623</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626613</v>
+        <v>626620</v>
       </c>
       <c r="R6" t="n">
-        <v>6997411</v>
+        <v>6997401</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314642</v>
+        <v>131314626</v>
       </c>
       <c r="B7" t="n">
-        <v>92131</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1192,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1282,10 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314641</v>
+        <v>131314642</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>92137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,31 +1297,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1325,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626582</v>
+        <v>626613</v>
       </c>
       <c r="R8" t="n">
-        <v>6997317</v>
+        <v>6997411</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,6 +1368,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1390,7 +1390,7 @@
         <v>131314637</v>
       </c>
       <c r="B9" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>131314624</v>
       </c>
       <c r="B10" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>131314644</v>
       </c>
       <c r="B11" t="n">
-        <v>80329</v>
+        <v>80331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>131314652</v>
       </c>
       <c r="B12" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>131314653</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>131314650</v>
       </c>
       <c r="B14" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314648</v>
+        <v>131314625</v>
       </c>
       <c r="B15" t="n">
-        <v>79264</v>
+        <v>91838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,37 +2010,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626483</v>
+        <v>626433</v>
       </c>
       <c r="R15" t="n">
-        <v>6997313</v>
+        <v>6997263</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2081,7 +2078,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2093,17 +2089,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314625</v>
+        <v>131314648</v>
       </c>
       <c r="B16" t="n">
-        <v>91832</v>
+        <v>79266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2111,34 +2107,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626433</v>
+        <v>626483</v>
       </c>
       <c r="R16" t="n">
-        <v>6997263</v>
+        <v>6997313</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2179,6 +2178,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2190,44 +2190,45 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131314621</v>
+        <v>131314630</v>
       </c>
       <c r="B17" t="n">
-        <v>91795</v>
+        <v>57904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2235,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626433</v>
+        <v>626458</v>
       </c>
       <c r="R17" t="n">
-        <v>6997263</v>
+        <v>6997294</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,13 +2274,17 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack tall</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2298,38 +2303,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131314630</v>
+        <v>131314621</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>91801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2337,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626458</v>
+        <v>626433</v>
       </c>
       <c r="R18" t="n">
-        <v>6997294</v>
+        <v>6997263</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,17 +2379,13 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack tall</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314636</v>
+        <v>131314631</v>
       </c>
       <c r="B19" t="n">
-        <v>58061</v>
+        <v>57904</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,42 +2415,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626574</v>
+        <v>626459</v>
       </c>
       <c r="R19" t="n">
-        <v>6997271</v>
+        <v>6997269</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,7 +2490,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2492,7 +2500,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2512,17 +2520,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314631</v>
+        <v>131314636</v>
       </c>
       <c r="B20" t="n">
-        <v>57902</v>
+        <v>58063</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,50 +2538,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626459</v>
+        <v>626574</v>
       </c>
       <c r="R20" t="n">
-        <v>6997269</v>
+        <v>6997271</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2645,7 +2645,7 @@
         <v>131314651</v>
       </c>
       <c r="B21" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>131314629</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>131314635</v>
       </c>
       <c r="B23" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>131314646</v>
       </c>
       <c r="B24" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>131314634</v>
       </c>
       <c r="B25" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>131314633</v>
       </c>
       <c r="B26" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>131314640</v>
       </c>
       <c r="B27" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131314647</v>
+        <v>131314627</v>
       </c>
       <c r="B28" t="n">
-        <v>79264</v>
+        <v>91838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>626607</v>
+        <v>626433</v>
       </c>
       <c r="R28" t="n">
-        <v>6997322</v>
+        <v>6997299</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131314627</v>
+        <v>131314647</v>
       </c>
       <c r="B29" t="n">
-        <v>91832</v>
+        <v>79266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>626433</v>
+        <v>626607</v>
       </c>
       <c r="R29" t="n">
-        <v>6997299</v>
+        <v>6997322</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3618,7 +3618,7 @@
         <v>131314638</v>
       </c>
       <c r="B30" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131314622</v>
+        <v>131314649</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>79266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626710</v>
+        <v>626421</v>
       </c>
       <c r="R2" t="n">
-        <v>6997373</v>
+        <v>6997282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -769,17 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131314649</v>
+        <v>131314622</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>91838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626421</v>
+        <v>626710</v>
       </c>
       <c r="R3" t="n">
-        <v>6997282</v>
+        <v>6997373</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -866,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1611,32 +1611,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314644</v>
+        <v>131314652</v>
       </c>
       <c r="B11" t="n">
-        <v>80331</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626648</v>
+        <v>626681</v>
       </c>
       <c r="R11" t="n">
-        <v>6997392</v>
+        <v>6997376</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314652</v>
+        <v>131314653</v>
       </c>
       <c r="B12" t="n">
         <v>79266</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626681</v>
+        <v>626421</v>
       </c>
       <c r="R12" t="n">
-        <v>6997376</v>
+        <v>6997267</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314653</v>
+        <v>131314650</v>
       </c>
       <c r="B13" t="n">
         <v>79266</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626421</v>
+        <v>626380</v>
       </c>
       <c r="R13" t="n">
-        <v>6997267</v>
+        <v>6997310</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,32 +1902,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131314650</v>
+        <v>131314644</v>
       </c>
       <c r="B14" t="n">
-        <v>79266</v>
+        <v>80331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626380</v>
+        <v>626648</v>
       </c>
       <c r="R14" t="n">
-        <v>6997310</v>
+        <v>6997392</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2197,38 +2197,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131314630</v>
+        <v>131314621</v>
       </c>
       <c r="B17" t="n">
-        <v>57904</v>
+        <v>91801</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2236,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626458</v>
+        <v>626433</v>
       </c>
       <c r="R17" t="n">
-        <v>6997294</v>
+        <v>6997263</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2274,17 +2273,13 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack tall</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2303,37 +2298,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131314621</v>
+        <v>131314630</v>
       </c>
       <c r="B18" t="n">
-        <v>91801</v>
+        <v>57904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2341,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626433</v>
+        <v>626458</v>
       </c>
       <c r="R18" t="n">
-        <v>6997263</v>
+        <v>6997294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,13 +2375,17 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314631</v>
+        <v>131314636</v>
       </c>
       <c r="B19" t="n">
-        <v>57904</v>
+        <v>58063</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,50 +2415,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626459</v>
+        <v>626574</v>
       </c>
       <c r="R19" t="n">
-        <v>6997269</v>
+        <v>6997271</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,7 +2482,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2500,7 +2492,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2520,17 +2512,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314636</v>
+        <v>131314631</v>
       </c>
       <c r="B20" t="n">
-        <v>58063</v>
+        <v>57904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,42 +2530,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626574</v>
+        <v>626459</v>
       </c>
       <c r="R20" t="n">
-        <v>6997271</v>
+        <v>6997269</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -1611,32 +1611,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314652</v>
+        <v>131314644</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>80331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626681</v>
+        <v>626648</v>
       </c>
       <c r="R11" t="n">
-        <v>6997376</v>
+        <v>6997392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314653</v>
+        <v>131314652</v>
       </c>
       <c r="B12" t="n">
         <v>79266</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626421</v>
+        <v>626681</v>
       </c>
       <c r="R12" t="n">
-        <v>6997267</v>
+        <v>6997376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131314650</v>
+        <v>131314653</v>
       </c>
       <c r="B13" t="n">
         <v>79266</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626380</v>
+        <v>626421</v>
       </c>
       <c r="R13" t="n">
-        <v>6997310</v>
+        <v>6997267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,32 +1902,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131314644</v>
+        <v>131314650</v>
       </c>
       <c r="B14" t="n">
-        <v>80331</v>
+        <v>79266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1937,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626648</v>
+        <v>626380</v>
       </c>
       <c r="R14" t="n">
-        <v>6997392</v>
+        <v>6997310</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2404,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314636</v>
+        <v>131314631</v>
       </c>
       <c r="B19" t="n">
-        <v>58063</v>
+        <v>57904</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2415,42 +2415,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626574</v>
+        <v>626459</v>
       </c>
       <c r="R19" t="n">
-        <v>6997271</v>
+        <v>6997269</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,7 +2490,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2492,7 +2500,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2512,17 +2520,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314631</v>
+        <v>131314636</v>
       </c>
       <c r="B20" t="n">
-        <v>57904</v>
+        <v>58063</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,50 +2538,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Söder om Rudtjärnbergets Naturreservat, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626459</v>
+        <v>626574</v>
       </c>
       <c r="R20" t="n">
-        <v>6997269</v>
+        <v>6997271</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131314641</v>
+        <v>131314623</v>
       </c>
       <c r="B5" t="n">
-        <v>57901</v>
+        <v>91838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,31 +990,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1022,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626582</v>
+        <v>626620</v>
       </c>
       <c r="R5" t="n">
-        <v>6997317</v>
+        <v>6997401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,6 +1061,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1077,14 +1073,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131314623</v>
+        <v>131314626</v>
       </c>
       <c r="B6" t="n">
         <v>91838</v>
@@ -1122,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626620</v>
+        <v>626613</v>
       </c>
       <c r="R6" t="n">
-        <v>6997401</v>
+        <v>6997411</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314626</v>
+        <v>131314642</v>
       </c>
       <c r="B7" t="n">
-        <v>91838</v>
+        <v>92137</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1192,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314642</v>
+        <v>131314641</v>
       </c>
       <c r="B8" t="n">
-        <v>92137</v>
+        <v>57901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,26 +1293,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1324,10 +1325,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626613</v>
+        <v>626582</v>
       </c>
       <c r="R8" t="n">
-        <v>6997411</v>
+        <v>6997317</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,7 +1369,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 61754-2025 artfynd.xlsx
+++ b/artfynd/A 61754-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314642</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314622</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314623</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314624</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314625</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314626</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314627</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314621</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314646</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1666,6 +1716,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314647</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,6 +1822,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314648</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314649</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1961,6 +2026,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314650</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2058,6 +2128,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314651</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2155,6 +2230,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314652</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2252,6 +2332,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314653</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2357,6 +2442,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314638</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2462,6 +2552,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314640</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2567,6 +2662,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314641</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2695,6 +2795,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314629</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2801,6 +2906,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314630</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2924,6 +3034,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314631</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3030,6 +3145,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314632</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3136,6 +3256,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314633</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3259,6 +3384,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314634</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3382,6 +3512,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314635</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3497,6 +3632,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314636</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3620,6 +3760,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314637</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3717,8 +3862,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314644</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>